--- a/analysis/results/store_level_metrics.xlsx
+++ b/analysis/results/store_level_metrics.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,41 +425,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>store_key</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>city</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>avg_category_price_index</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>median_price_deviation</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>price_volatility_score</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>price_leadership_frequency_pct</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>products_count</t>
         </is>
@@ -465,19 +477,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>1.0413</v>
       </c>
       <c r="D2" t="n">
-        <v>-171.83</v>
+        <v>-238.91</v>
       </c>
       <c r="E2" t="n">
-        <v>26.04</v>
+        <v>33.35</v>
       </c>
       <c r="F2" t="n">
-        <v>63.01</v>
+        <v>61.2</v>
       </c>
       <c r="G2" t="n">
-        <v>74</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +504,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>1.0413</v>
       </c>
       <c r="D3" t="n">
-        <v>-171.83</v>
+        <v>-238.91</v>
       </c>
       <c r="E3" t="n">
-        <v>26.04</v>
+        <v>33.35</v>
       </c>
       <c r="F3" t="n">
-        <v>63.01</v>
+        <v>61.2</v>
       </c>
       <c r="G3" t="n">
-        <v>74</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4">
@@ -519,19 +531,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>1.0413</v>
       </c>
       <c r="D4" t="n">
-        <v>-171.83</v>
+        <v>-238.91</v>
       </c>
       <c r="E4" t="n">
-        <v>26.04</v>
+        <v>33.35</v>
       </c>
       <c r="F4" t="n">
-        <v>63.01</v>
+        <v>61.2</v>
       </c>
       <c r="G4" t="n">
-        <v>74</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5">
@@ -546,19 +558,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>1.0413</v>
       </c>
       <c r="D5" t="n">
-        <v>-171.83</v>
+        <v>-238.91</v>
       </c>
       <c r="E5" t="n">
-        <v>26.04</v>
+        <v>33.35</v>
       </c>
       <c r="F5" t="n">
-        <v>63.01</v>
+        <v>61.2</v>
       </c>
       <c r="G5" t="n">
-        <v>74</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">
@@ -573,19 +585,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>1.0413</v>
       </c>
       <c r="D6" t="n">
-        <v>-171.83</v>
+        <v>-238.91</v>
       </c>
       <c r="E6" t="n">
-        <v>26.04</v>
+        <v>33.35</v>
       </c>
       <c r="F6" t="n">
-        <v>63.01</v>
+        <v>61.2</v>
       </c>
       <c r="G6" t="n">
-        <v>74</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7">
@@ -603,16 +615,16 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-360.16</v>
+        <v>-619.88</v>
       </c>
       <c r="E7" t="n">
-        <v>31.7</v>
+        <v>31.61</v>
       </c>
       <c r="F7" t="n">
-        <v>59.09</v>
+        <v>36.68</v>
       </c>
       <c r="G7" t="n">
-        <v>75</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -630,16 +642,16 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-360.16</v>
+        <v>-619.88</v>
       </c>
       <c r="E8" t="n">
-        <v>31.7</v>
+        <v>31.61</v>
       </c>
       <c r="F8" t="n">
-        <v>59.09</v>
+        <v>36.68</v>
       </c>
       <c r="G8" t="n">
-        <v>75</v>
+        <v>556</v>
       </c>
     </row>
     <row r="9">
@@ -657,97 +669,97 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-360.16</v>
+        <v>-619.88</v>
       </c>
       <c r="E9" t="n">
-        <v>31.7</v>
+        <v>31.61</v>
       </c>
       <c r="F9" t="n">
-        <v>59.09</v>
+        <v>36.68</v>
       </c>
       <c r="G9" t="n">
-        <v>75</v>
+        <v>556</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>jalalsons</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>faisalabad</t>
+          <t>islamabad</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9923</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>-69.89</v>
+        <v>-472.83</v>
       </c>
       <c r="E10" t="n">
-        <v>24.56</v>
+        <v>24.7</v>
       </c>
       <c r="F10" t="n">
-        <v>62.73</v>
+        <v>58.82</v>
       </c>
       <c r="G10" t="n">
-        <v>628</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>jalalsons</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>islamabad</t>
+          <t>karachi</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9923</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>-69.89</v>
+        <v>-472.83</v>
       </c>
       <c r="E11" t="n">
-        <v>24.56</v>
+        <v>24.7</v>
       </c>
       <c r="F11" t="n">
-        <v>62.73</v>
+        <v>58.82</v>
       </c>
       <c r="G11" t="n">
-        <v>628</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>metro</t>
+          <t>jalalsons</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>karachi</t>
+          <t>lahore</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9923</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>-69.89</v>
+        <v>-472.83</v>
       </c>
       <c r="E12" t="n">
-        <v>24.56</v>
+        <v>24.7</v>
       </c>
       <c r="F12" t="n">
-        <v>62.73</v>
+        <v>58.82</v>
       </c>
       <c r="G12" t="n">
-        <v>628</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13">
@@ -758,104 +770,104 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>lahore</t>
+          <t>faisalabad</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9923</v>
+        <v>1.0101</v>
       </c>
       <c r="D13" t="n">
-        <v>-69.89</v>
+        <v>-41.06</v>
       </c>
       <c r="E13" t="n">
-        <v>24.56</v>
+        <v>26.4</v>
       </c>
       <c r="F13" t="n">
-        <v>62.73</v>
+        <v>56.82</v>
       </c>
       <c r="G13" t="n">
-        <v>628</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>naheed</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hyderabad</t>
+          <t>islamabad</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.0062</v>
+        <v>1.0101</v>
       </c>
       <c r="D14" t="n">
-        <v>-58.09</v>
+        <v>-41.06</v>
       </c>
       <c r="E14" t="n">
-        <v>23.13</v>
+        <v>26.4</v>
       </c>
       <c r="F14" t="n">
-        <v>34.87</v>
+        <v>56.82</v>
       </c>
       <c r="G14" t="n">
-        <v>617</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>naheed</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>islamabad</t>
+          <t>karachi</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.0062</v>
+        <v>1.0101</v>
       </c>
       <c r="D15" t="n">
-        <v>-58.09</v>
+        <v>-41.06</v>
       </c>
       <c r="E15" t="n">
-        <v>23.13</v>
+        <v>26.4</v>
       </c>
       <c r="F15" t="n">
-        <v>34.87</v>
+        <v>56.82</v>
       </c>
       <c r="G15" t="n">
-        <v>617</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>naheed</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>karachi</t>
+          <t>lahore</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.0062</v>
+        <v>1.0101</v>
       </c>
       <c r="D16" t="n">
-        <v>-58.09</v>
+        <v>-41.06</v>
       </c>
       <c r="E16" t="n">
-        <v>23.13</v>
+        <v>26.4</v>
       </c>
       <c r="F16" t="n">
-        <v>34.87</v>
+        <v>56.82</v>
       </c>
       <c r="G16" t="n">
-        <v>617</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17">
@@ -866,23 +878,104 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>hyderabad</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-123.08</v>
+      </c>
+      <c r="E17" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="G17" t="n">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>naheed</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>islamabad</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-123.08</v>
+      </c>
+      <c r="E18" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="F18" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="G18" t="n">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>naheed</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>karachi</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-123.08</v>
+      </c>
+      <c r="E19" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="G19" t="n">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>naheed</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>lahore</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>0.997</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-57.07</v>
-      </c>
-      <c r="E17" t="n">
-        <v>23.14</v>
-      </c>
-      <c r="F17" t="n">
-        <v>34.93</v>
-      </c>
-      <c r="G17" t="n">
-        <v>616</v>
+      <c r="C20" t="n">
+        <v>0.9913999999999999</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-117.78</v>
+      </c>
+      <c r="E20" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="G20" t="n">
+        <v>529</v>
       </c>
     </row>
   </sheetData>

--- a/analysis/results/store_level_metrics.xlsx
+++ b/analysis/results/store_level_metrics.xlsx
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.0413</v>
+        <v>1.0808</v>
       </c>
       <c r="D2" t="n">
-        <v>-238.91</v>
+        <v>-251.42</v>
       </c>
       <c r="E2" t="n">
-        <v>33.35</v>
+        <v>35.77</v>
       </c>
       <c r="F2" t="n">
-        <v>61.2</v>
+        <v>59.11</v>
       </c>
       <c r="G2" t="n">
-        <v>250</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3">
@@ -504,19 +504,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.0413</v>
+        <v>1.0808</v>
       </c>
       <c r="D3" t="n">
-        <v>-238.91</v>
+        <v>-251.42</v>
       </c>
       <c r="E3" t="n">
-        <v>33.35</v>
+        <v>35.77</v>
       </c>
       <c r="F3" t="n">
-        <v>61.2</v>
+        <v>59.11</v>
       </c>
       <c r="G3" t="n">
-        <v>250</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4">
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.0413</v>
+        <v>1.0808</v>
       </c>
       <c r="D4" t="n">
-        <v>-238.91</v>
+        <v>-251.42</v>
       </c>
       <c r="E4" t="n">
-        <v>33.35</v>
+        <v>35.77</v>
       </c>
       <c r="F4" t="n">
-        <v>61.2</v>
+        <v>59.11</v>
       </c>
       <c r="G4" t="n">
-        <v>250</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5">
@@ -558,19 +558,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.0413</v>
+        <v>1.0808</v>
       </c>
       <c r="D5" t="n">
-        <v>-238.91</v>
+        <v>-251.42</v>
       </c>
       <c r="E5" t="n">
-        <v>33.35</v>
+        <v>35.77</v>
       </c>
       <c r="F5" t="n">
-        <v>61.2</v>
+        <v>59.11</v>
       </c>
       <c r="G5" t="n">
-        <v>250</v>
+        <v>304</v>
       </c>
     </row>
     <row r="6">
@@ -585,19 +585,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.0413</v>
+        <v>1.0808</v>
       </c>
       <c r="D6" t="n">
-        <v>-238.91</v>
+        <v>-251.42</v>
       </c>
       <c r="E6" t="n">
-        <v>33.35</v>
+        <v>35.77</v>
       </c>
       <c r="F6" t="n">
-        <v>61.2</v>
+        <v>59.11</v>
       </c>
       <c r="G6" t="n">
-        <v>250</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7">
@@ -615,16 +615,16 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-619.88</v>
+        <v>-544.34</v>
       </c>
       <c r="E7" t="n">
-        <v>31.61</v>
+        <v>37.37</v>
       </c>
       <c r="F7" t="n">
-        <v>36.68</v>
+        <v>37.92</v>
       </c>
       <c r="G7" t="n">
-        <v>556</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="8">
@@ -642,16 +642,16 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-619.88</v>
+        <v>-544.34</v>
       </c>
       <c r="E8" t="n">
-        <v>31.61</v>
+        <v>37.37</v>
       </c>
       <c r="F8" t="n">
-        <v>36.68</v>
+        <v>37.92</v>
       </c>
       <c r="G8" t="n">
-        <v>556</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="9">
@@ -669,16 +669,16 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-619.88</v>
+        <v>-544.34</v>
       </c>
       <c r="E9" t="n">
-        <v>31.61</v>
+        <v>37.37</v>
       </c>
       <c r="F9" t="n">
-        <v>36.68</v>
+        <v>37.92</v>
       </c>
       <c r="G9" t="n">
-        <v>556</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="10">
@@ -693,19 +693,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>-472.83</v>
+        <v>-766.15</v>
       </c>
       <c r="E10" t="n">
-        <v>24.7</v>
+        <v>34.03</v>
       </c>
       <c r="F10" t="n">
-        <v>58.82</v>
+        <v>60.97</v>
       </c>
       <c r="G10" t="n">
-        <v>276</v>
+        <v>489</v>
       </c>
     </row>
     <row r="11">
@@ -720,19 +720,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>-472.83</v>
+        <v>-766.15</v>
       </c>
       <c r="E11" t="n">
-        <v>24.7</v>
+        <v>34.03</v>
       </c>
       <c r="F11" t="n">
-        <v>58.82</v>
+        <v>60.97</v>
       </c>
       <c r="G11" t="n">
-        <v>276</v>
+        <v>489</v>
       </c>
     </row>
     <row r="12">
@@ -747,19 +747,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>-472.83</v>
+        <v>-766.15</v>
       </c>
       <c r="E12" t="n">
-        <v>24.7</v>
+        <v>34.03</v>
       </c>
       <c r="F12" t="n">
-        <v>58.82</v>
+        <v>60.97</v>
       </c>
       <c r="G12" t="n">
-        <v>276</v>
+        <v>489</v>
       </c>
     </row>
     <row r="13">
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.0101</v>
+        <v>1.0066</v>
       </c>
       <c r="D13" t="n">
-        <v>-41.06</v>
+        <v>-38.78</v>
       </c>
       <c r="E13" t="n">
-        <v>26.4</v>
+        <v>31.35</v>
       </c>
       <c r="F13" t="n">
-        <v>56.82</v>
+        <v>56.8</v>
       </c>
       <c r="G13" t="n">
-        <v>288</v>
+        <v>362</v>
       </c>
     </row>
     <row r="14">
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.0101</v>
+        <v>1.0066</v>
       </c>
       <c r="D14" t="n">
-        <v>-41.06</v>
+        <v>-38.78</v>
       </c>
       <c r="E14" t="n">
-        <v>26.4</v>
+        <v>31.35</v>
       </c>
       <c r="F14" t="n">
-        <v>56.82</v>
+        <v>56.8</v>
       </c>
       <c r="G14" t="n">
-        <v>288</v>
+        <v>362</v>
       </c>
     </row>
     <row r="15">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.0101</v>
+        <v>1.0066</v>
       </c>
       <c r="D15" t="n">
-        <v>-41.06</v>
+        <v>-38.78</v>
       </c>
       <c r="E15" t="n">
-        <v>26.4</v>
+        <v>31.35</v>
       </c>
       <c r="F15" t="n">
-        <v>56.82</v>
+        <v>56.8</v>
       </c>
       <c r="G15" t="n">
-        <v>288</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16">
@@ -855,19 +855,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.0101</v>
+        <v>1.0066</v>
       </c>
       <c r="D16" t="n">
-        <v>-41.06</v>
+        <v>-38.78</v>
       </c>
       <c r="E16" t="n">
-        <v>26.4</v>
+        <v>31.35</v>
       </c>
       <c r="F16" t="n">
-        <v>56.82</v>
+        <v>56.8</v>
       </c>
       <c r="G16" t="n">
-        <v>288</v>
+        <v>362</v>
       </c>
     </row>
     <row r="17">
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9755</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>-123.08</v>
+        <v>-123.34</v>
       </c>
       <c r="E17" t="n">
-        <v>24.83</v>
+        <v>24.79</v>
       </c>
       <c r="F17" t="n">
-        <v>42.86</v>
+        <v>42.76</v>
       </c>
       <c r="G17" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="18">
@@ -909,19 +909,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9755</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>-123.08</v>
+        <v>-123.34</v>
       </c>
       <c r="E18" t="n">
-        <v>24.83</v>
+        <v>24.79</v>
       </c>
       <c r="F18" t="n">
-        <v>42.86</v>
+        <v>42.76</v>
       </c>
       <c r="G18" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="19">
@@ -936,19 +936,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9755</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>-123.08</v>
+        <v>-123.34</v>
       </c>
       <c r="E19" t="n">
-        <v>24.83</v>
+        <v>24.79</v>
       </c>
       <c r="F19" t="n">
-        <v>42.86</v>
+        <v>42.76</v>
       </c>
       <c r="G19" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="20">
@@ -963,19 +963,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9931</v>
       </c>
       <c r="D20" t="n">
-        <v>-117.78</v>
+        <v>-120.43</v>
       </c>
       <c r="E20" t="n">
-        <v>24.83</v>
+        <v>24.79</v>
       </c>
       <c r="F20" t="n">
-        <v>42.86</v>
+        <v>42.76</v>
       </c>
       <c r="G20" t="n">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
   </sheetData>
